--- a/branches/Richard/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T21:01:51+00:00</t>
+    <t>2023-05-06T12:10:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-06T12:10:27+00:00</t>
+    <t>2023-05-06T12:11:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-06T12:11:33+00:00</t>
+    <t>2023-05-07T12:05:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T12:05:50+00:00</t>
+    <t>2023-05-07T12:06:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T12:06:01+00:00</t>
+    <t>2023-05-07T12:57:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T12:57:45+00:00</t>
+    <t>2023-05-07T12:58:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T12:58:10+00:00</t>
+    <t>2023-05-07T13:06:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T13:06:46+00:00</t>
+    <t>2023-05-07T13:07:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T13:07:20+00:00</t>
+    <t>2023-05-07T13:57:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T13:57:21+00:00</t>
+    <t>2023-05-08T06:55:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T06:55:13+00:00</t>
+    <t>2023-05-08T06:55:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T06:55:26+00:00</t>
+    <t>2023-05-08T13:44:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T13:44:54+00:00</t>
+    <t>2023-05-08T13:51:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T13:51:23+00:00</t>
+    <t>2023-05-08T14:05:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T14:05:33+00:00</t>
+    <t>2023-05-08T14:07:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T14:07:06+00:00</t>
+    <t>2023-05-08T14:23:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T14:23:05+00:00</t>
+    <t>2023-05-08T14:48:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T14:48:00+00:00</t>
+    <t>2023-05-08T15:19:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T15:19:54+00:00</t>
+    <t>2023-05-08T15:31:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T15:31:47+00:00</t>
+    <t>2023-05-08T16:10:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T16:10:55+00:00</t>
+    <t>2023-05-08T18:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T18:38:59+00:00</t>
+    <t>2023-05-08T18:49:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T18:49:00+00:00</t>
+    <t>2023-05-08T19:06:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:06:08+00:00</t>
+    <t>2023-05-08T19:17:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:17:16+00:00</t>
+    <t>2023-05-08T19:36:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:36:32+00:00</t>
+    <t>2023-05-08T19:37:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:37:24+00:00</t>
+    <t>2023-05-08T19:39:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:39:41+00:00</t>
+    <t>2023-05-08T19:40:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:40:43+00:00</t>
+    <t>2023-05-08T19:42:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:42:22+00:00</t>
+    <t>2023-05-08T19:53:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:53:59+00:00</t>
+    <t>2023-05-08T21:00:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T21:00:30+00:00</t>
+    <t>2023-05-08T21:01:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-arv-treatment.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3510" uniqueCount="646">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3508" uniqueCount="647">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T21:01:17+00:00</t>
+    <t>2023-05-09T15:00:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -96,7 +96,7 @@
     <t>FHIR Version</t>
   </si>
   <si>
-    <t>4.0.1</t>
+    <t>4.3.0</t>
   </si>
   <si>
     <t>Kind</t>
@@ -278,6 +278,9 @@
     <t>Act[classCode=PCPR, moodCode=INT]</t>
   </si>
   <si>
+    <t>clinical.careprovision</t>
+  </si>
+  <si>
     <t>CarePlan.id</t>
   </si>
   <si>
@@ -361,7 +364,7 @@
     <t>preferred</t>
   </si>
   <si>
-    <t>A human language.</t>
+    <t>IETF language tag</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/languages</t>
@@ -419,6 +422,10 @@
     <t>DomainResource.contained</t>
   </si>
   <si>
+    <t xml:space="preserve">dom-r4b:Containing new R4B resources within R4 resources may cause interoperability issues if instances are shared with R4 systems {($this is Citation or $this is Evidence or $this is EvidenceReport or $this is EvidenceVariable or $this is MedicinalProductDefinition or $this is PackagedProductDefinition or $this is AdministrableProductDefinition or $this is Ingredient or $this is ClinicalUseDefinition or $this is RegulatedAuthorization or $this is SubstanceDefinition or $this is SubscriptionStatus or $this is SubscriptionTopic) implies (%resource is Citation or %resource is Evidence or %resource is EvidenceReport or %resource is EvidenceVariable or %resource is MedicinalProductDefinition or %resource is PackagedProductDefinition or %resource is AdministrableProductDefinition or %resource is Ingredient or %resource is ClinicalUseDefinition or %resource is RegulatedAuthorization or %resource is SubstanceDefinition or %resource is SubscriptionStatus or %resource is SubscriptionTopic)}
+</t>
+  </si>
+  <si>
     <t>N/A</t>
   </si>
   <si>
@@ -459,7 +466,7 @@
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension).</t>
   </si>
   <si>
     <t>DomainResource.modifierExtension</t>
@@ -478,7 +485,7 @@
     <t>Business identifiers assigned to this care plan by the performer or other systems which remain constant as the resource is updated and propagates from server to server.</t>
   </si>
   <si>
-    <t>This is a business identifier, not a resource identifier (see [discussion](http://hl7.org/fhir/R4/resource.html#identifiers)).  It is best practice for the identifier to only appear on a single resource instance, however business practices may occasionally dictate that multiple resource instances with the same identifier can exist - possibly even with different resource types.  For example, multiple Patient and a Person resource instance might share the same social insurance number.</t>
+    <t>This is a business identifier, not a resource identifier (see [discussion](http://hl7.org/fhir/R4B/resource.html#identifiers)).  It is best practice for the identifier to only appear on a single resource instance, however business practices may occasionally dictate that multiple resource instances with the same identifier can exist - possibly even with different resource types.  For example, multiple Patient and a Person resource instance might share the same social insurance number.</t>
   </si>
   <si>
     <t>Allows identification of the care plan as it is known by various participating systems and in a way that remains consistent across servers.</t>
@@ -518,205 +525,199 @@
     <t>CarePlan.identifier.id</t>
   </si>
   <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>CarePlan.identifier:PLAC.extension</t>
+  </si>
+  <si>
+    <t>CarePlan.identifier.extension</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>CarePlan.identifier:PLAC.use</t>
+  </si>
+  <si>
+    <t>CarePlan.identifier.use</t>
+  </si>
+  <si>
+    <t>usual | official | temp | secondary | old (If known)</t>
+  </si>
+  <si>
+    <t>The purpose of this identifier.</t>
+  </si>
+  <si>
+    <t>Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
+  </si>
+  <si>
+    <t>Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-use|4.3.0</t>
+  </si>
+  <si>
+    <t>Identifier.use</t>
+  </si>
+  <si>
+    <t>Role.code or implied by context</t>
+  </si>
+  <si>
+    <t>CarePlan.identifier:PLAC.type</t>
+  </si>
+  <si>
+    <t>CarePlan.identifier.type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeableConcept
+</t>
+  </si>
+  <si>
+    <t>Description of identifier</t>
+  </si>
+  <si>
+    <t>A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
+  </si>
+  <si>
+    <t>Allows users to make use of identifiers when the identifier system is not known.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+  </si>
+  <si>
+    <t>Identifier.type</t>
+  </si>
+  <si>
+    <t>CX.5</t>
+  </si>
+  <si>
+    <t>CarePlan.identifier:PLAC.type.id</t>
+  </si>
+  <si>
+    <t>CarePlan.identifier.type.id</t>
+  </si>
+  <si>
+    <t>CarePlan.identifier:PLAC.type.extension</t>
+  </si>
+  <si>
+    <t>CarePlan.identifier.type.extension</t>
+  </si>
+  <si>
+    <t>CarePlan.identifier:PLAC.type.coding</t>
+  </si>
+  <si>
+    <t>CarePlan.identifier.type.coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>CarePlan.identifier:PLAC.type.coding.id</t>
+  </si>
+  <si>
+    <t>CarePlan.identifier.type.coding.id</t>
+  </si>
+  <si>
+    <t>CarePlan.identifier:PLAC.type.coding.extension</t>
+  </si>
+  <si>
+    <t>CarePlan.identifier.type.coding.extension</t>
+  </si>
+  <si>
+    <t>CarePlan.identifier:PLAC.type.coding.system</t>
+  </si>
+  <si>
+    <t>CarePlan.identifier.type.coding.system</t>
+  </si>
+  <si>
+    <t>Identity of the terminology system</t>
+  </si>
+  <si>
+    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
+  </si>
+  <si>
+    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
+  </si>
+  <si>
+    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
+  </si>
+  <si>
+    <t>http://terminology.hl7.org/CodeSystem/v2-0203</t>
+  </si>
+  <si>
+    <t>Coding.system</t>
+  </si>
+  <si>
+    <t>./codeSystem</t>
+  </si>
+  <si>
+    <t>C*E.3</t>
+  </si>
+  <si>
+    <t>CarePlan.identifier:PLAC.type.coding.version</t>
+  </si>
+  <si>
+    <t>CarePlan.identifier.type.coding.version</t>
+  </si>
+  <si>
     <t xml:space="preserve">string
 </t>
   </si>
   <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
-    <t>CarePlan.identifier:PLAC.extension</t>
-  </si>
-  <si>
-    <t>CarePlan.identifier.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
-    <t>CarePlan.identifier:PLAC.use</t>
-  </si>
-  <si>
-    <t>CarePlan.identifier.use</t>
-  </si>
-  <si>
-    <t>usual | official | temp | secondary | old (If known)</t>
-  </si>
-  <si>
-    <t>The purpose of this identifier.</t>
-  </si>
-  <si>
-    <t>Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
-  </si>
-  <si>
-    <t>Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
-  </si>
-  <si>
-    <t>required</t>
-  </si>
-  <si>
-    <t>Identifies the purpose for this identifier, if known .</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-use|4.0.1</t>
-  </si>
-  <si>
-    <t>Identifier.use</t>
-  </si>
-  <si>
-    <t>Role.code or implied by context</t>
-  </si>
-  <si>
-    <t>CarePlan.identifier:PLAC.type</t>
-  </si>
-  <si>
-    <t>CarePlan.identifier.type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CodeableConcept
-</t>
-  </si>
-  <si>
-    <t>Description of identifier</t>
-  </si>
-  <si>
-    <t>A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
-  </si>
-  <si>
-    <t>This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
-  </si>
-  <si>
-    <t>Allows users to make use of identifiers when the identifier system is not known.</t>
-  </si>
-  <si>
-    <t>extensible</t>
-  </si>
-  <si>
-    <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
-  </si>
-  <si>
-    <t>Identifier.type</t>
-  </si>
-  <si>
-    <t>CX.5</t>
-  </si>
-  <si>
-    <t>CarePlan.identifier:PLAC.type.id</t>
-  </si>
-  <si>
-    <t>CarePlan.identifier.type.id</t>
-  </si>
-  <si>
-    <t>CarePlan.identifier:PLAC.type.extension</t>
-  </si>
-  <si>
-    <t>CarePlan.identifier.type.extension</t>
-  </si>
-  <si>
-    <t>CarePlan.identifier:PLAC.type.coding</t>
-  </si>
-  <si>
-    <t>CarePlan.identifier.type.coding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
-    <t>Code defined by a terminology system</t>
-  </si>
-  <si>
-    <t>A reference to a code defined by a terminology system.</t>
-  </si>
-  <si>
-    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
-  </si>
-  <si>
-    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>union(., ./translation)</t>
-  </si>
-  <si>
-    <t>C*E.1-8, C*E.10-22</t>
-  </si>
-  <si>
-    <t>CarePlan.identifier:PLAC.type.coding.id</t>
-  </si>
-  <si>
-    <t>CarePlan.identifier.type.coding.id</t>
-  </si>
-  <si>
-    <t>CarePlan.identifier:PLAC.type.coding.extension</t>
-  </si>
-  <si>
-    <t>CarePlan.identifier.type.coding.extension</t>
-  </si>
-  <si>
-    <t>CarePlan.identifier:PLAC.type.coding.system</t>
-  </si>
-  <si>
-    <t>CarePlan.identifier.type.coding.system</t>
-  </si>
-  <si>
-    <t>Identity of the terminology system</t>
-  </si>
-  <si>
-    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
-  </si>
-  <si>
-    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
-  </si>
-  <si>
-    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
-  </si>
-  <si>
-    <t>http://terminology.hl7.org/CodeSystem/v2-0203</t>
-  </si>
-  <si>
-    <t>Coding.system</t>
-  </si>
-  <si>
-    <t>./codeSystem</t>
-  </si>
-  <si>
-    <t>C*E.3</t>
-  </si>
-  <si>
-    <t>CarePlan.identifier:PLAC.type.coding.version</t>
-  </si>
-  <si>
-    <t>CarePlan.identifier.type.coding.version</t>
-  </si>
-  <si>
     <t>Version of the system - if relevant</t>
   </si>
   <si>
@@ -892,7 +893,7 @@
     <t>The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
   </si>
   <si>
-    <t>If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
+    <t>If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4B/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
   </si>
   <si>
     <t>123456</t>
@@ -1067,7 +1068,7 @@
     <t>Allows clinicians to determine whether the plan is actionable or not.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/request-status|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/request-status|4.3.0</t>
   </si>
   <si>
     <t>Request.status {uses different ValueSet}</t>
@@ -1100,7 +1101,7 @@
     <t>Codes indicating the degree of authority/intentionality associated with a care plan.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/care-plan-intent|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/care-plan-intent|4.3.0</t>
   </si>
   <si>
     <t>Request.intent</t>
@@ -1528,7 +1529,7 @@
     <t>The details of the proposed activity represented in a specific resource.</t>
   </si>
   <si>
-    <t>Standard extension exists ([resource-pertainsToGoal](http://hl7.org/fhir/R4/extension-resource-pertainstogoal.html)) that allows goals to be referenced from any of the referenced resources in CarePlan.activity.reference.  +    <t>Standard extension exists ([resource-pertainsToGoal](http://hl7.org/fhir/R4B/extension-resource-pertainstogoal.html)) that allows goals to be referenced from any of the referenced resources in CarePlan.activity.reference.   The goal should be visible when the resource referenced by CarePlan.activity.reference is viewed independently from the CarePlan.  Requests that are pointed to by a CarePlan using this element should *not* point to this CarePlan using the "basedOn" element.  i.e. Requests that are part of a CarePlan are not "based on" the CarePlan.</t>
   </si>
   <si>
@@ -1589,6 +1590,10 @@
 </t>
   </si>
   <si>
+    <t>ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
     <t>CarePlan.activity.detail.modifierExtension</t>
   </si>
   <si>
@@ -1610,7 +1615,7 @@
     <t>Resource types defined as part of FHIR that can be represented as in-line definitions of a care plan activity.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/care-plan-activity-kind|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/care-plan-activity-kind|4.3.0</t>
   </si>
   <si>
     <t>.inboundRelationship[typeCode=COMP].source[classCode=LIST].code</t>
@@ -1757,7 +1762,7 @@
     <t>Codes that reflect the current state of a care plan activity within its overall life cycle.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/care-plan-activity-status|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/care-plan-activity-status|4.3.0</t>
   </si>
   <si>
     <t>Request.status</t>
@@ -2602,7 +2607,7 @@
         <v>85</v>
       </c>
       <c r="AM2" t="s" s="2">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="AN2" t="s" s="2">
         <v>80</v>
@@ -2610,10 +2615,10 @@
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -2624,7 +2629,7 @@
         <v>78</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>80</v>
@@ -2633,19 +2638,19 @@
         <v>80</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N3" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -2695,13 +2700,13 @@
         <v>80</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>80</v>
@@ -2724,10 +2729,10 @@
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -2738,7 +2743,7 @@
         <v>78</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>80</v>
@@ -2747,16 +2752,16 @@
         <v>80</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -2807,19 +2812,19 @@
         <v>80</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>80</v>
@@ -2836,10 +2841,10 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2850,28 +2855,28 @@
         <v>78</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2921,19 +2926,19 @@
         <v>80</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>80</v>
@@ -2950,10 +2955,10 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2964,7 +2969,7 @@
         <v>78</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>80</v>
@@ -2976,16 +2981,16 @@
         <v>80</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -3011,13 +3016,13 @@
         <v>80</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>80</v>
@@ -3035,19 +3040,19 @@
         <v>80</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>80</v>
@@ -3064,21 +3069,21 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>80</v>
@@ -3090,16 +3095,16 @@
         <v>80</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -3149,25 +3154,25 @@
         <v>80</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AM7" t="s" s="2">
         <v>80</v>
@@ -3178,14 +3183,14 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -3204,16 +3209,16 @@
         <v>80</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -3263,7 +3268,7 @@
         <v>80</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>78</v>
@@ -3275,13 +3280,13 @@
         <v>80</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>80</v>
+        <v>131</v>
       </c>
       <c r="AK8" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="AM8" t="s" s="2">
         <v>80</v>
@@ -3292,14 +3297,14 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -3318,16 +3323,16 @@
         <v>80</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -3377,7 +3382,7 @@
         <v>80</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>78</v>
@@ -3389,13 +3394,13 @@
         <v>80</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="AM9" t="s" s="2">
         <v>80</v>
@@ -3406,14 +3411,14 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
@@ -3426,25 +3431,25 @@
         <v>80</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J10" t="s" s="2">
         <v>80</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O10" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>80</v>
@@ -3493,7 +3498,7 @@
         <v>80</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>
@@ -3505,13 +3510,13 @@
         <v>80</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="AM10" t="s" s="2">
         <v>80</v>
@@ -3522,10 +3527,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -3533,7 +3538,7 @@
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G11" t="s" s="2">
         <v>79</v>
@@ -3545,22 +3550,22 @@
         <v>80</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="O11" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>80</v>
@@ -3597,19 +3602,19 @@
         <v>80</v>
       </c>
       <c r="AB11" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="AC11" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="AD11" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE11" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
@@ -3621,40 +3626,40 @@
         <v>80</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D12" t="s" s="2">
         <v>80</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>80</v>
@@ -3663,22 +3668,22 @@
         <v>80</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="O12" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>80</v>
@@ -3727,7 +3732,7 @@
         <v>80</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
@@ -3739,27 +3744,27 @@
         <v>80</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3770,7 +3775,7 @@
         <v>78</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>80</v>
@@ -3782,13 +3787,13 @@
         <v>80</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>161</v>
+        <v>90</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -3839,13 +3844,13 @@
         <v>80</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>80</v>
@@ -3857,7 +3862,7 @@
         <v>80</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AM13" t="s" s="2">
         <v>80</v>
@@ -3868,14 +3873,14 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
@@ -3894,16 +3899,16 @@
         <v>80</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3941,19 +3946,19 @@
         <v>80</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AC14" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AD14" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -3965,13 +3970,13 @@
         <v>80</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AM14" t="s" s="2">
         <v>80</v>
@@ -3982,10 +3987,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3996,31 +4001,31 @@
         <v>78</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>80</v>
@@ -4045,11 +4050,9 @@
         <v>80</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="Y15" t="s" s="2">
         <v>180</v>
       </c>
+      <c r="Y15" s="2"/>
       <c r="Z15" t="s" s="2">
         <v>181</v>
       </c>
@@ -4075,13 +4078,13 @@
         <v>78</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>80</v>
@@ -4093,7 +4096,7 @@
         <v>80</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="16" hidden="true">
@@ -4112,7 +4115,7 @@
         <v>78</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>80</v>
@@ -4121,7 +4124,7 @@
         <v>80</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K16" t="s" s="2">
         <v>186</v>
@@ -4163,41 +4166,39 @@
       <c r="X16" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="Y16" t="s" s="2">
+      <c r="Y16" s="2"/>
+      <c r="Z16" t="s" s="2">
         <v>192</v>
       </c>
-      <c r="Z16" t="s" s="2">
+      <c r="AA16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF16" t="s" s="2">
         <v>193</v>
       </c>
-      <c r="AA16" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB16" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC16" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD16" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF16" t="s" s="2">
-        <v>194</v>
-      </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>80</v>
@@ -4209,15 +4210,15 @@
         <v>80</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="B17" t="s" s="2">
         <v>196</v>
-      </c>
-      <c r="B17" t="s" s="2">
-        <v>197</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4228,7 +4229,7 @@
         <v>78</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>80</v>
@@ -4240,13 +4241,13 @@
         <v>80</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>161</v>
+        <v>90</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -4297,13 +4298,13 @@
         <v>80</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>80</v>
@@ -4315,7 +4316,7 @@
         <v>80</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>80</v>
@@ -4326,14 +4327,14 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="B18" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="B18" t="s" s="2">
-        <v>199</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -4352,16 +4353,16 @@
         <v>80</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -4399,19 +4400,19 @@
         <v>80</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -4423,13 +4424,13 @@
         <v>80</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>80</v>
@@ -4440,10 +4441,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="B19" t="s" s="2">
         <v>200</v>
-      </c>
-      <c r="B19" t="s" s="2">
-        <v>201</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4463,22 +4464,22 @@
         <v>80</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>202</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="M19" t="s" s="2">
         <v>203</v>
       </c>
-      <c r="M19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="N19" t="s" s="2">
+      <c r="O19" t="s" s="2">
         <v>205</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>206</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>80</v>
@@ -4527,7 +4528,7 @@
         <v>80</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -4539,27 +4540,27 @@
         <v>80</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL19" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="AM19" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN19" t="s" s="2">
         <v>208</v>
-      </c>
-      <c r="AM19" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN19" t="s" s="2">
-        <v>209</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="B20" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="B20" t="s" s="2">
-        <v>211</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4570,7 +4571,7 @@
         <v>78</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>80</v>
@@ -4582,13 +4583,13 @@
         <v>80</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>161</v>
+        <v>90</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4639,13 +4640,13 @@
         <v>80</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>80</v>
@@ -4657,7 +4658,7 @@
         <v>80</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>80</v>
@@ -4668,14 +4669,14 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="B21" t="s" s="2">
         <v>212</v>
-      </c>
-      <c r="B21" t="s" s="2">
-        <v>213</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -4694,16 +4695,16 @@
         <v>80</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4741,19 +4742,19 @@
         <v>80</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -4765,13 +4766,13 @@
         <v>80</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>80</v>
@@ -4782,10 +4783,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="B22" t="s" s="2">
         <v>214</v>
-      </c>
-      <c r="B22" t="s" s="2">
-        <v>215</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4796,7 +4797,7 @@
         <v>78</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>80</v>
@@ -4805,22 +4806,22 @@
         <v>80</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L22" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>216</v>
       </c>
-      <c r="M22" t="s" s="2">
+      <c r="N22" t="s" s="2">
         <v>217</v>
       </c>
-      <c r="N22" t="s" s="2">
+      <c r="O22" t="s" s="2">
         <v>218</v>
-      </c>
-      <c r="O22" t="s" s="2">
-        <v>219</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>80</v>
@@ -4830,78 +4831,78 @@
         <v>80</v>
       </c>
       <c r="S22" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="T22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF22" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="T22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF22" t="s" s="2">
+      <c r="AG22" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH22" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ22" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL22" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="AG22" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH22" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ22" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL22" t="s" s="2">
+      <c r="AM22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN22" t="s" s="2">
         <v>222</v>
-      </c>
-      <c r="AM22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN22" t="s" s="2">
-        <v>223</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="B23" t="s" s="2">
         <v>224</v>
-      </c>
-      <c r="B23" t="s" s="2">
-        <v>225</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4912,7 +4913,7 @@
         <v>78</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>80</v>
@@ -4921,10 +4922,10 @@
         <v>80</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>161</v>
+        <v>225</v>
       </c>
       <c r="L23" t="s" s="2">
         <v>226</v>
@@ -4989,13 +4990,13 @@
         <v>78</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>80</v>
@@ -5026,7 +5027,7 @@
         <v>78</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>80</v>
@@ -5035,10 +5036,10 @@
         <v>80</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L24" t="s" s="2">
         <v>234</v>
@@ -5058,7 +5059,7 @@
         <v>80</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>80</v>
@@ -5103,13 +5104,13 @@
         <v>78</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>80</v>
@@ -5140,7 +5141,7 @@
         <v>78</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>80</v>
@@ -5149,10 +5150,10 @@
         <v>80</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>161</v>
+        <v>225</v>
       </c>
       <c r="L25" t="s" s="2">
         <v>242</v>
@@ -5217,13 +5218,13 @@
         <v>78</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>80</v>
@@ -5254,7 +5255,7 @@
         <v>78</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>80</v>
@@ -5263,7 +5264,7 @@
         <v>80</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K26" t="s" s="2">
         <v>251</v>
@@ -5333,13 +5334,13 @@
         <v>78</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>80</v>
@@ -5370,7 +5371,7 @@
         <v>78</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>80</v>
@@ -5379,10 +5380,10 @@
         <v>80</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>161</v>
+        <v>225</v>
       </c>
       <c r="L27" t="s" s="2">
         <v>261</v>
@@ -5449,13 +5450,13 @@
         <v>78</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>80</v>
@@ -5483,10 +5484,10 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>80</v>
@@ -5495,10 +5496,10 @@
         <v>80</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L28" t="s" s="2">
         <v>271</v>
@@ -5565,13 +5566,13 @@
         <v>78</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>80</v>
@@ -5599,10 +5600,10 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>80</v>
@@ -5611,10 +5612,10 @@
         <v>80</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>161</v>
+        <v>225</v>
       </c>
       <c r="L29" t="s" s="2">
         <v>282</v>
@@ -5679,13 +5680,13 @@
         <v>78</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>80</v>
@@ -5716,7 +5717,7 @@
         <v>78</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>80</v>
@@ -5725,7 +5726,7 @@
         <v>80</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K30" t="s" s="2">
         <v>291</v>
@@ -5791,13 +5792,13 @@
         <v>78</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>80</v>
@@ -5828,7 +5829,7 @@
         <v>78</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>80</v>
@@ -5837,7 +5838,7 @@
         <v>80</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K31" t="s" s="2">
         <v>299</v>
@@ -5905,13 +5906,13 @@
         <v>78</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>80</v>
@@ -5951,7 +5952,7 @@
         <v>80</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K32" t="s" s="2">
         <v>307</v>
@@ -6023,7 +6024,7 @@
         <v>80</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>310</v>
@@ -6063,10 +6064,10 @@
         <v>80</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L33" t="s" s="2">
         <v>313</v>
@@ -6137,7 +6138,7 @@
         <v>80</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>316</v>
@@ -6177,7 +6178,7 @@
         <v>80</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K34" t="s" s="2">
         <v>319</v>
@@ -6251,7 +6252,7 @@
         <v>80</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>323</v>
@@ -6291,7 +6292,7 @@
         <v>80</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K35" t="s" s="2">
         <v>319</v>
@@ -6367,7 +6368,7 @@
         <v>80</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>330</v>
@@ -6407,7 +6408,7 @@
         <v>80</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K36" t="s" s="2">
         <v>319</v>
@@ -6481,7 +6482,7 @@
         <v>80</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>80</v>
@@ -6509,22 +6510,22 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I37" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L37" t="s" s="2">
         <v>336</v>
@@ -6561,7 +6562,7 @@
         <v>80</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Y37" t="s" s="2">
         <v>337</v>
@@ -6588,16 +6589,16 @@
         <v>335</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>341</v>
@@ -6625,22 +6626,22 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I38" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L38" t="s" s="2">
         <v>346</v>
@@ -6677,7 +6678,7 @@
         <v>80</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Y38" t="s" s="2">
         <v>350</v>
@@ -6704,16 +6705,16 @@
         <v>345</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>352</v>
@@ -6753,7 +6754,7 @@
         <v>80</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K39" t="s" s="2">
         <v>186</v>
@@ -6829,7 +6830,7 @@
         <v>80</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>80</v>
@@ -6860,7 +6861,7 @@
         <v>78</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>80</v>
@@ -6869,10 +6870,10 @@
         <v>80</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>161</v>
+        <v>225</v>
       </c>
       <c r="L40" t="s" s="2">
         <v>363</v>
@@ -6935,13 +6936,13 @@
         <v>78</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>80</v>
@@ -6972,7 +6973,7 @@
         <v>78</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>80</v>
@@ -6981,10 +6982,10 @@
         <v>80</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>161</v>
+        <v>225</v>
       </c>
       <c r="L41" t="s" s="2">
         <v>366</v>
@@ -7049,13 +7050,13 @@
         <v>78</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>80</v>
@@ -7083,10 +7084,10 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>80</v>
@@ -7095,7 +7096,7 @@
         <v>80</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K42" t="s" s="2">
         <v>372</v>
@@ -7158,16 +7159,16 @@
         <v>370</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>375</v>
@@ -7195,10 +7196,10 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>80</v>
@@ -7207,7 +7208,7 @@
         <v>80</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K43" t="s" s="2">
         <v>380</v>
@@ -7275,13 +7276,13 @@
         <v>78</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>384</v>
@@ -7309,10 +7310,10 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>80</v>
@@ -7321,7 +7322,7 @@
         <v>80</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K44" t="s" s="2">
         <v>291</v>
@@ -7391,13 +7392,13 @@
         <v>78</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>394</v>
@@ -7428,7 +7429,7 @@
         <v>78</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>80</v>
@@ -7437,7 +7438,7 @@
         <v>80</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K45" t="s" s="2">
         <v>400</v>
@@ -7503,13 +7504,13 @@
         <v>78</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>403</v>
@@ -7540,7 +7541,7 @@
         <v>78</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>80</v>
@@ -7549,7 +7550,7 @@
         <v>80</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K46" t="s" s="2">
         <v>407</v>
@@ -7617,13 +7618,13 @@
         <v>78</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>411</v>
@@ -7737,7 +7738,7 @@
         <v>80</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>80</v>
@@ -7851,7 +7852,7 @@
         <v>80</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>422</v>
@@ -7891,7 +7892,7 @@
         <v>80</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K49" t="s" s="2">
         <v>425</v>
@@ -7967,7 +7968,7 @@
         <v>80</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>430</v>
@@ -8083,7 +8084,7 @@
         <v>80</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>440</v>
@@ -8199,7 +8200,7 @@
         <v>80</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>80</v>
@@ -8227,7 +8228,7 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G52" t="s" s="2">
         <v>79</v>
@@ -8344,7 +8345,7 @@
         <v>78</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>80</v>
@@ -8356,13 +8357,13 @@
         <v>80</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>161</v>
+        <v>225</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8413,13 +8414,13 @@
         <v>80</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>80</v>
@@ -8431,7 +8432,7 @@
         <v>80</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>80</v>
@@ -8449,7 +8450,7 @@
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8468,16 +8469,16 @@
         <v>80</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8527,7 +8528,7 @@
         <v>80</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -8539,13 +8540,13 @@
         <v>80</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>80</v>
@@ -8576,13 +8577,13 @@
         <v>80</v>
       </c>
       <c r="I55" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="L55" t="s" s="2">
         <v>460</v>
@@ -8591,10 +8592,10 @@
         <v>461</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>80</v>
@@ -8655,13 +8656,13 @@
         <v>80</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>80</v>
@@ -8769,7 +8770,7 @@
         <v>80</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>80</v>
@@ -8885,7 +8886,7 @@
         <v>80</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>474</v>
@@ -9001,7 +9002,7 @@
         <v>80</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>80</v>
@@ -9032,7 +9033,7 @@
         <v>78</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>80</v>
@@ -9111,13 +9112,13 @@
         <v>78</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>490</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>491</v>
@@ -9148,7 +9149,7 @@
         <v>78</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>80</v>
@@ -9225,7 +9226,7 @@
         <v>78</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>490</v>
@@ -9262,7 +9263,7 @@
         <v>78</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>80</v>
@@ -9274,13 +9275,13 @@
         <v>80</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>161</v>
+        <v>225</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9331,13 +9332,13 @@
         <v>80</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>80</v>
@@ -9349,7 +9350,7 @@
         <v>80</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>80</v>
@@ -9386,7 +9387,7 @@
         <v>80</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="L62" t="s" s="2">
         <v>499</v>
@@ -9431,17 +9432,17 @@
         <v>80</v>
       </c>
       <c r="AB62" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AC62" s="2"/>
       <c r="AD62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE62" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -9453,7 +9454,7 @@
         <v>80</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>80</v>
@@ -9486,10 +9487,10 @@
         <v>78</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I63" t="s" s="2">
         <v>80</v>
@@ -9555,7 +9556,7 @@
         <v>80</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -9567,7 +9568,7 @@
         <v>506</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>138</v>
+        <v>507</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>80</v>
@@ -9584,10 +9585,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9604,13 +9605,13 @@
         <v>80</v>
       </c>
       <c r="I64" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="L64" t="s" s="2">
         <v>460</v>
@@ -9619,10 +9620,10 @@
         <v>461</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>80</v>
@@ -9683,13 +9684,13 @@
         <v>80</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>80</v>
@@ -9700,10 +9701,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9714,10 +9715,10 @@
         <v>78</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I65" t="s" s="2">
         <v>80</v>
@@ -9726,17 +9727,17 @@
         <v>80</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>80</v>
@@ -9746,7 +9747,7 @@
         <v>80</v>
       </c>
       <c r="S65" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="T65" t="s" s="2">
         <v>80</v>
@@ -9761,13 +9762,13 @@
         <v>80</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>80</v>
@@ -9785,25 +9786,25 @@
         <v>80</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>80</v>
@@ -9814,10 +9815,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9840,17 +9841,17 @@
         <v>80</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="L66" t="s" s="2">
         <v>308</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>80</v>
@@ -9899,7 +9900,7 @@
         <v>80</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -9911,7 +9912,7 @@
         <v>80</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>310</v>
@@ -9928,10 +9929,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9954,19 +9955,19 @@
         <v>80</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L67" t="s" s="2">
         <v>313</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="N67" t="s" s="2">
         <v>315</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>80</v>
@@ -10015,7 +10016,7 @@
         <v>80</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
@@ -10027,7 +10028,7 @@
         <v>80</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>316</v>
@@ -10044,10 +10045,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10058,10 +10059,10 @@
         <v>78</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H68" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I68" t="s" s="2">
         <v>80</v>
@@ -10073,16 +10074,16 @@
         <v>186</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>80</v>
@@ -10107,11 +10108,11 @@
         <v>80</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Y68" s="2"/>
       <c r="Z68" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>80</v>
@@ -10129,39 +10130,39 @@
         <v>80</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10172,7 +10173,7 @@
         <v>78</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>80</v>
@@ -10184,13 +10185,13 @@
         <v>80</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>161</v>
+        <v>90</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10241,13 +10242,13 @@
         <v>80</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>80</v>
@@ -10259,7 +10260,7 @@
         <v>80</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>80</v>
@@ -10270,14 +10271,14 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -10296,16 +10297,16 @@
         <v>80</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -10343,19 +10344,19 @@
         <v>80</v>
       </c>
       <c r="AB70" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AC70" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AD70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE70" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -10367,13 +10368,13 @@
         <v>80</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>80</v>
@@ -10384,10 +10385,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10407,22 +10408,22 @@
         <v>80</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K71" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="L71" t="s" s="2">
         <v>202</v>
       </c>
-      <c r="L71" t="s" s="2">
+      <c r="M71" t="s" s="2">
         <v>203</v>
       </c>
-      <c r="M71" t="s" s="2">
+      <c r="N71" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="N71" t="s" s="2">
+      <c r="O71" t="s" s="2">
         <v>205</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>206</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>80</v>
@@ -10471,7 +10472,7 @@
         <v>80</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
@@ -10483,27 +10484,27 @@
         <v>80</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL71" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="AM71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN71" t="s" s="2">
         <v>208</v>
-      </c>
-      <c r="AM71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN71" t="s" s="2">
-        <v>209</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10514,7 +10515,7 @@
         <v>78</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>80</v>
@@ -10523,10 +10524,10 @@
         <v>80</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>161</v>
+        <v>225</v>
       </c>
       <c r="L72" t="s" s="2">
         <v>261</v>
@@ -10548,7 +10549,7 @@
         <v>80</v>
       </c>
       <c r="S72" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="T72" t="s" s="2">
         <v>80</v>
@@ -10593,13 +10594,13 @@
         <v>78</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>80</v>
@@ -10616,10 +10617,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10630,10 +10631,10 @@
         <v>78</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H73" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I73" t="s" s="2">
         <v>80</v>
@@ -10645,13 +10646,13 @@
         <v>186</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -10677,11 +10678,11 @@
         <v>80</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Y73" s="2"/>
       <c r="Z73" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>80</v>
@@ -10699,7 +10700,7 @@
         <v>80</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
@@ -10711,10 +10712,10 @@
         <v>80</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AL73" t="s" s="2">
         <v>80</v>
@@ -10728,10 +10729,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10742,7 +10743,7 @@
         <v>78</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>80</v>
@@ -10754,13 +10755,13 @@
         <v>80</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>161</v>
+        <v>90</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -10811,13 +10812,13 @@
         <v>80</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>80</v>
@@ -10829,7 +10830,7 @@
         <v>80</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>80</v>
@@ -10840,14 +10841,14 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
@@ -10866,16 +10867,16 @@
         <v>80</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -10913,19 +10914,19 @@
         <v>80</v>
       </c>
       <c r="AB75" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AC75" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AD75" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE75" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
@@ -10937,13 +10938,13 @@
         <v>80</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>80</v>
@@ -10954,10 +10955,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10977,22 +10978,22 @@
         <v>80</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K76" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="L76" t="s" s="2">
         <v>202</v>
       </c>
-      <c r="L76" t="s" s="2">
+      <c r="M76" t="s" s="2">
         <v>203</v>
       </c>
-      <c r="M76" t="s" s="2">
+      <c r="N76" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="N76" t="s" s="2">
+      <c r="O76" t="s" s="2">
         <v>205</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>206</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>80</v>
@@ -11041,7 +11042,7 @@
         <v>80</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>78</v>
@@ -11053,27 +11054,27 @@
         <v>80</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL76" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="AM76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN76" t="s" s="2">
         <v>208</v>
-      </c>
-      <c r="AM76" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN76" t="s" s="2">
-        <v>209</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11084,7 +11085,7 @@
         <v>78</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>80</v>
@@ -11093,10 +11094,10 @@
         <v>80</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>161</v>
+        <v>225</v>
       </c>
       <c r="L77" t="s" s="2">
         <v>261</v>
@@ -11118,7 +11119,7 @@
         <v>80</v>
       </c>
       <c r="S77" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="T77" t="s" s="2">
         <v>80</v>
@@ -11163,13 +11164,13 @@
         <v>78</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>80</v>
@@ -11186,10 +11187,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11212,16 +11213,16 @@
         <v>80</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -11271,7 +11272,7 @@
         <v>80</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
@@ -11283,7 +11284,7 @@
         <v>80</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>430</v>
@@ -11300,10 +11301,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11329,14 +11330,14 @@
         <v>442</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>80</v>
@@ -11385,7 +11386,7 @@
         <v>80</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
@@ -11397,7 +11398,7 @@
         <v>80</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>80</v>
@@ -11414,10 +11415,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11425,34 +11426,34 @@
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I80" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J80" t="s" s="2">
         <v>80</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>80</v>
@@ -11477,13 +11478,13 @@
         <v>80</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>80</v>
@@ -11501,39 +11502,39 @@
         <v>80</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="AG80" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AM80" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11544,7 +11545,7 @@
         <v>78</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>80</v>
@@ -11559,13 +11560,13 @@
         <v>186</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -11615,22 +11616,22 @@
         <v>80</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AL81" t="s" s="2">
         <v>80</v>
@@ -11644,10 +11645,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11658,13 +11659,13 @@
         <v>78</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I82" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J82" t="s" s="2">
         <v>80</v>
@@ -11673,85 +11674,85 @@
         <v>251</v>
       </c>
       <c r="L82" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="M82" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="N82" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="O82" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="P82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q82" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="R82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF82" t="s" s="2">
         <v>572</v>
       </c>
-      <c r="M82" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>574</v>
-      </c>
-      <c r="O82" t="s" s="2">
-        <v>575</v>
-      </c>
-      <c r="P82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q82" t="s" s="2">
-        <v>576</v>
-      </c>
-      <c r="R82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF82" t="s" s="2">
-        <v>571</v>
-      </c>
       <c r="AG82" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>80</v>
@@ -11762,10 +11763,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11776,7 +11777,7 @@
         <v>78</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>80</v>
@@ -11788,17 +11789,17 @@
         <v>80</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>80</v>
@@ -11835,29 +11836,29 @@
         <v>80</v>
       </c>
       <c r="AB83" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AC83" s="2"/>
       <c r="AD83" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE83" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>394</v>
@@ -11869,18 +11870,18 @@
         <v>80</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C84" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="D84" t="s" s="2">
         <v>80</v>
@@ -11890,7 +11891,7 @@
         <v>78</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>80</v>
@@ -11905,14 +11906,14 @@
         <v>291</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>80</v>
@@ -11961,19 +11962,19 @@
         <v>80</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>394</v>
@@ -11985,15 +11986,15 @@
         <v>80</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12004,7 +12005,7 @@
         <v>78</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>80</v>
@@ -12016,19 +12017,19 @@
         <v>80</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>80</v>
@@ -12077,39 +12078,39 @@
         <v>80</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12132,19 +12133,19 @@
         <v>80</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>80</v>
@@ -12193,7 +12194,7 @@
         <v>80</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>78</v>
@@ -12205,27 +12206,27 @@
         <v>80</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12236,7 +12237,7 @@
         <v>78</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>80</v>
@@ -12248,13 +12249,13 @@
         <v>80</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -12284,61 +12285,61 @@
         <v>358</v>
       </c>
       <c r="Y87" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="Z87" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AB87" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AC87" s="2"/>
       <c r="AD87" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE87" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C88" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="D88" t="s" s="2">
         <v>80</v>
@@ -12348,10 +12349,10 @@
         <v>78</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H88" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I88" t="s" s="2">
         <v>80</v>
@@ -12363,10 +12364,10 @@
         <v>186</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -12393,11 +12394,11 @@
         <v>80</v>
       </c>
       <c r="X88" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Y88" s="2"/>
       <c r="Z88" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>80</v>
@@ -12415,39 +12416,39 @@
         <v>80</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="AM88" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12458,7 +12459,7 @@
         <v>78</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>80</v>
@@ -12470,13 +12471,13 @@
         <v>80</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>161</v>
+        <v>90</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -12527,13 +12528,13 @@
         <v>80</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI89" t="s" s="2">
         <v>80</v>
@@ -12545,7 +12546,7 @@
         <v>80</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>80</v>
@@ -12556,14 +12557,14 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
@@ -12582,16 +12583,16 @@
         <v>80</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -12629,19 +12630,19 @@
         <v>80</v>
       </c>
       <c r="AB90" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AC90" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AD90" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE90" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>78</v>
@@ -12653,13 +12654,13 @@
         <v>80</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>80</v>
@@ -12670,10 +12671,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12693,22 +12694,22 @@
         <v>80</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K91" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="L91" t="s" s="2">
         <v>202</v>
       </c>
-      <c r="L91" t="s" s="2">
+      <c r="M91" t="s" s="2">
         <v>203</v>
       </c>
-      <c r="M91" t="s" s="2">
+      <c r="N91" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="N91" t="s" s="2">
+      <c r="O91" t="s" s="2">
         <v>205</v>
-      </c>
-      <c r="O91" t="s" s="2">
-        <v>206</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>80</v>
@@ -12757,7 +12758,7 @@
         <v>80</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>78</v>
@@ -12769,27 +12770,27 @@
         <v>80</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL91" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="AM91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN91" t="s" s="2">
         <v>208</v>
-      </c>
-      <c r="AM91" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN91" t="s" s="2">
-        <v>209</v>
       </c>
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12800,7 +12801,7 @@
         <v>78</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H92" t="s" s="2">
         <v>80</v>
@@ -12809,10 +12810,10 @@
         <v>80</v>
       </c>
       <c r="J92" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>161</v>
+        <v>225</v>
       </c>
       <c r="L92" t="s" s="2">
         <v>261</v>
@@ -12834,7 +12835,7 @@
         <v>80</v>
       </c>
       <c r="S92" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="T92" t="s" s="2">
         <v>80</v>
@@ -12879,13 +12880,13 @@
         <v>78</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI92" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK92" t="s" s="2">
         <v>80</v>
@@ -12902,21 +12903,21 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>80</v>
@@ -12928,17 +12929,17 @@
         <v>80</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>80</v>
@@ -12987,39 +12988,39 @@
         <v>80</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI93" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK93" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="AM93" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13030,7 +13031,7 @@
         <v>78</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H94" t="s" s="2">
         <v>80</v>
@@ -13042,13 +13043,13 @@
         <v>80</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -13099,39 +13100,39 @@
         <v>80</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI94" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="AM94" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13142,7 +13143,7 @@
         <v>78</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>80</v>
@@ -13154,13 +13155,13 @@
         <v>80</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>161</v>
+        <v>225</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -13211,25 +13212,25 @@
         <v>80</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI95" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="AM95" t="s" s="2">
         <v>80</v>
@@ -13240,10 +13241,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13254,7 +13255,7 @@
         <v>78</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>80</v>
@@ -13269,14 +13270,14 @@
         <v>477</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>80</v>
@@ -13325,7 +13326,7 @@
         <v>80</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>78</v>
@@ -13337,10 +13338,10 @@
         <v>80</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="AL96" t="s" s="2">
         <v>482</v>

--- a/branches/Richard/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-09T15:00:51+00:00</t>
+    <t>2023-05-09T15:03:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-arv-treatment.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3508" uniqueCount="647">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3510" uniqueCount="646">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-09T15:03:02+00:00</t>
+    <t>2023-05-09T15:34:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -96,7 +96,7 @@
     <t>FHIR Version</t>
   </si>
   <si>
-    <t>4.3.0</t>
+    <t>4.0.1</t>
   </si>
   <si>
     <t>Kind</t>
@@ -278,9 +278,6 @@
     <t>Act[classCode=PCPR, moodCode=INT]</t>
   </si>
   <si>
-    <t>clinical.careprovision</t>
-  </si>
-  <si>
     <t>CarePlan.id</t>
   </si>
   <si>
@@ -364,7 +361,7 @@
     <t>preferred</t>
   </si>
   <si>
-    <t>IETF language tag</t>
+    <t>A human language.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/languages</t>
@@ -422,10 +419,6 @@
     <t>DomainResource.contained</t>
   </si>
   <si>
-    <t xml:space="preserve">dom-r4b:Containing new R4B resources within R4 resources may cause interoperability issues if instances are shared with R4 systems {($this is Citation or $this is Evidence or $this is EvidenceReport or $this is EvidenceVariable or $this is MedicinalProductDefinition or $this is PackagedProductDefinition or $this is AdministrableProductDefinition or $this is Ingredient or $this is ClinicalUseDefinition or $this is RegulatedAuthorization or $this is SubstanceDefinition or $this is SubscriptionStatus or $this is SubscriptionTopic) implies (%resource is Citation or %resource is Evidence or %resource is EvidenceReport or %resource is EvidenceVariable or %resource is MedicinalProductDefinition or %resource is PackagedProductDefinition or %resource is AdministrableProductDefinition or %resource is Ingredient or %resource is ClinicalUseDefinition or %resource is RegulatedAuthorization or %resource is SubstanceDefinition or %resource is SubscriptionStatus or %resource is SubscriptionTopic)}
-</t>
-  </si>
-  <si>
     <t>N/A</t>
   </si>
   <si>
@@ -466,7 +459,7 @@
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension).</t>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
   </si>
   <si>
     <t>DomainResource.modifierExtension</t>
@@ -485,7 +478,7 @@
     <t>Business identifiers assigned to this care plan by the performer or other systems which remain constant as the resource is updated and propagates from server to server.</t>
   </si>
   <si>
-    <t>This is a business identifier, not a resource identifier (see [discussion](http://hl7.org/fhir/R4B/resource.html#identifiers)).  It is best practice for the identifier to only appear on a single resource instance, however business practices may occasionally dictate that multiple resource instances with the same identifier can exist - possibly even with different resource types.  For example, multiple Patient and a Person resource instance might share the same social insurance number.</t>
+    <t>This is a business identifier, not a resource identifier (see [discussion](http://hl7.org/fhir/R4/resource.html#identifiers)).  It is best practice for the identifier to only appear on a single resource instance, however business practices may occasionally dictate that multiple resource instances with the same identifier can exist - possibly even with different resource types.  For example, multiple Patient and a Person resource instance might share the same social insurance number.</t>
   </si>
   <si>
     <t>Allows identification of the care plan as it is known by various participating systems and in a way that remains consistent across servers.</t>
@@ -525,6 +518,10 @@
     <t>CarePlan.identifier.id</t>
   </si>
   <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
     <t>Unique id for inter-element referencing</t>
   </si>
   <si>
@@ -580,7 +577,10 @@
     <t>required</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-use|4.3.0</t>
+    <t>Identifies the purpose for this identifier, if known .</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-use|4.0.1</t>
   </si>
   <si>
     <t>Identifier.use</t>
@@ -614,6 +614,9 @@
     <t>extensible</t>
   </si>
   <si>
+    <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
     <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
   </si>
   <si>
@@ -714,10 +717,6 @@
     <t>CarePlan.identifier.type.coding.version</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
     <t>Version of the system - if relevant</t>
   </si>
   <si>
@@ -893,7 +892,7 @@
     <t>The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
   </si>
   <si>
-    <t>If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4B/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
+    <t>If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
   </si>
   <si>
     <t>123456</t>
@@ -1068,7 +1067,7 @@
     <t>Allows clinicians to determine whether the plan is actionable or not.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/request-status|4.3.0</t>
+    <t>http://hl7.org/fhir/ValueSet/request-status|4.0.1</t>
   </si>
   <si>
     <t>Request.status {uses different ValueSet}</t>
@@ -1101,7 +1100,7 @@
     <t>Codes indicating the degree of authority/intentionality associated with a care plan.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/care-plan-intent|4.3.0</t>
+    <t>http://hl7.org/fhir/ValueSet/care-plan-intent|4.0.1</t>
   </si>
   <si>
     <t>Request.intent</t>
@@ -1529,7 +1528,7 @@
     <t>The details of the proposed activity represented in a specific resource.</t>
   </si>
   <si>
-    <t>Standard extension exists ([resource-pertainsToGoal](http://hl7.org/fhir/R4B/extension-resource-pertainstogoal.html)) that allows goals to be referenced from any of the referenced resources in CarePlan.activity.reference.  +    <t>Standard extension exists ([resource-pertainsToGoal](http://hl7.org/fhir/R4/extension-resource-pertainstogoal.html)) that allows goals to be referenced from any of the referenced resources in CarePlan.activity.reference.   The goal should be visible when the resource referenced by CarePlan.activity.reference is viewed independently from the CarePlan.  Requests that are pointed to by a CarePlan using this element should *not* point to this CarePlan using the "basedOn" element.  i.e. Requests that are part of a CarePlan are not "based on" the CarePlan.</t>
   </si>
   <si>
@@ -1590,10 +1589,6 @@
 </t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
     <t>CarePlan.activity.detail.modifierExtension</t>
   </si>
   <si>
@@ -1615,7 +1610,7 @@
     <t>Resource types defined as part of FHIR that can be represented as in-line definitions of a care plan activity.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/care-plan-activity-kind|4.3.0</t>
+    <t>http://hl7.org/fhir/ValueSet/care-plan-activity-kind|4.0.1</t>
   </si>
   <si>
     <t>.inboundRelationship[typeCode=COMP].source[classCode=LIST].code</t>
@@ -1762,7 +1757,7 @@
     <t>Codes that reflect the current state of a care plan activity within its overall life cycle.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/care-plan-activity-status|4.3.0</t>
+    <t>http://hl7.org/fhir/ValueSet/care-plan-activity-status|4.0.1</t>
   </si>
   <si>
     <t>Request.status</t>
@@ -2607,7 +2602,7 @@
         <v>85</v>
       </c>
       <c r="AM2" t="s" s="2">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="AN2" t="s" s="2">
         <v>80</v>
@@ -2615,10 +2610,10 @@
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -2629,28 +2624,28 @@
         <v>78</v>
       </c>
       <c r="G3" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H3" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I3" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J3" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="H3" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I3" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J3" t="s" s="2">
+      <c r="K3" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="K3" t="s" s="2">
+      <c r="L3" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="L3" t="s" s="2">
+      <c r="M3" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="M3" t="s" s="2">
+      <c r="N3" t="s" s="2">
         <v>92</v>
-      </c>
-      <c r="N3" t="s" s="2">
-        <v>93</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -2700,13 +2695,13 @@
         <v>80</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>80</v>
@@ -2729,10 +2724,10 @@
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -2743,25 +2738,25 @@
         <v>78</v>
       </c>
       <c r="G4" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H4" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I4" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J4" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="H4" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I4" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J4" t="s" s="2">
-        <v>89</v>
-      </c>
       <c r="K4" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="L4" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="L4" t="s" s="2">
+      <c r="M4" t="s" s="2">
         <v>97</v>
-      </c>
-      <c r="M4" t="s" s="2">
-        <v>98</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -2812,19 +2807,19 @@
         <v>80</v>
       </c>
       <c r="AF4" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AG4" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH4" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI4" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ4" t="s" s="2">
         <v>99</v>
-      </c>
-      <c r="AG4" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH4" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI4" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ4" t="s" s="2">
-        <v>100</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>80</v>
@@ -2841,10 +2836,10 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2855,28 +2850,28 @@
         <v>78</v>
       </c>
       <c r="G5" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H5" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I5" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="H5" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I5" t="s" s="2">
-        <v>89</v>
-      </c>
       <c r="J5" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K5" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L5" t="s" s="2">
         <v>102</v>
       </c>
-      <c r="L5" t="s" s="2">
+      <c r="M5" t="s" s="2">
         <v>103</v>
       </c>
-      <c r="M5" t="s" s="2">
+      <c r="N5" t="s" s="2">
         <v>104</v>
-      </c>
-      <c r="N5" t="s" s="2">
-        <v>105</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2926,19 +2921,19 @@
         <v>80</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>80</v>
@@ -2955,10 +2950,10 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2969,7 +2964,7 @@
         <v>78</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>80</v>
@@ -2981,16 +2976,16 @@
         <v>80</v>
       </c>
       <c r="K6" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L6" t="s" s="2">
         <v>108</v>
       </c>
-      <c r="L6" t="s" s="2">
+      <c r="M6" t="s" s="2">
         <v>109</v>
       </c>
-      <c r="M6" t="s" s="2">
+      <c r="N6" t="s" s="2">
         <v>110</v>
-      </c>
-      <c r="N6" t="s" s="2">
-        <v>111</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -3016,43 +3011,43 @@
         <v>80</v>
       </c>
       <c r="X6" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="Y6" t="s" s="2">
         <v>112</v>
       </c>
-      <c r="Y6" t="s" s="2">
+      <c r="Z6" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="Z6" t="s" s="2">
+      <c r="AA6" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB6" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC6" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD6" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE6" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF6" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="AA6" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB6" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD6" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE6" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF6" t="s" s="2">
-        <v>115</v>
-      </c>
       <c r="AG6" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>80</v>
@@ -3069,21 +3064,21 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>80</v>
@@ -3095,16 +3090,16 @@
         <v>80</v>
       </c>
       <c r="K7" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="L7" t="s" s="2">
         <v>118</v>
       </c>
-      <c r="L7" t="s" s="2">
+      <c r="M7" t="s" s="2">
         <v>119</v>
       </c>
-      <c r="M7" t="s" s="2">
+      <c r="N7" t="s" s="2">
         <v>120</v>
-      </c>
-      <c r="N7" t="s" s="2">
-        <v>121</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -3154,25 +3149,25 @@
         <v>80</v>
       </c>
       <c r="AF7" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="AG7" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH7" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI7" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ7" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK7" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL7" t="s" s="2">
         <v>122</v>
-      </c>
-      <c r="AG7" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH7" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI7" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ7" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK7" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL7" t="s" s="2">
-        <v>123</v>
       </c>
       <c r="AM7" t="s" s="2">
         <v>80</v>
@@ -3183,14 +3178,14 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -3209,16 +3204,16 @@
         <v>80</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="L8" t="s" s="2">
         <v>126</v>
       </c>
-      <c r="L8" t="s" s="2">
+      <c r="M8" t="s" s="2">
         <v>127</v>
       </c>
-      <c r="M8" t="s" s="2">
+      <c r="N8" t="s" s="2">
         <v>128</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>129</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -3268,7 +3263,7 @@
         <v>80</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>78</v>
@@ -3280,13 +3275,13 @@
         <v>80</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>131</v>
+        <v>80</v>
       </c>
       <c r="AK8" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="AM8" t="s" s="2">
         <v>80</v>
@@ -3297,14 +3292,14 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -3323,16 +3318,16 @@
         <v>80</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L9" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="M9" t="s" s="2">
         <v>135</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="N9" t="s" s="2">
         <v>136</v>
-      </c>
-      <c r="M9" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>138</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -3382,7 +3377,7 @@
         <v>80</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>78</v>
@@ -3394,13 +3389,13 @@
         <v>80</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="AM9" t="s" s="2">
         <v>80</v>
@@ -3411,14 +3406,14 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
@@ -3431,25 +3426,25 @@
         <v>80</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J10" t="s" s="2">
         <v>80</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="L10" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="M10" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="N10" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="O10" t="s" s="2">
         <v>142</v>
-      </c>
-      <c r="M10" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O10" t="s" s="2">
-        <v>144</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>80</v>
@@ -3498,7 +3493,7 @@
         <v>80</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>
@@ -3510,13 +3505,13 @@
         <v>80</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="AM10" t="s" s="2">
         <v>80</v>
@@ -3527,10 +3522,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -3538,7 +3533,7 @@
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G11" t="s" s="2">
         <v>79</v>
@@ -3550,22 +3545,22 @@
         <v>80</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K11" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="L11" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="M11" t="s" s="2">
         <v>147</v>
       </c>
-      <c r="L11" t="s" s="2">
+      <c r="N11" t="s" s="2">
         <v>148</v>
       </c>
-      <c r="M11" t="s" s="2">
+      <c r="O11" t="s" s="2">
         <v>149</v>
-      </c>
-      <c r="N11" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="O11" t="s" s="2">
-        <v>151</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>80</v>
@@ -3602,19 +3597,19 @@
         <v>80</v>
       </c>
       <c r="AB11" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="AC11" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="AD11" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE11" t="s" s="2">
         <v>152</v>
       </c>
-      <c r="AC11" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="AD11" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE11" t="s" s="2">
-        <v>154</v>
-      </c>
       <c r="AF11" t="s" s="2">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
@@ -3626,64 +3621,64 @@
         <v>80</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK11" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AL11" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="AM11" t="s" s="2">
         <v>155</v>
       </c>
-      <c r="AL11" t="s" s="2">
+      <c r="AN11" t="s" s="2">
         <v>156</v>
-      </c>
-      <c r="AM11" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="AN11" t="s" s="2">
-        <v>158</v>
       </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D12" t="s" s="2">
         <v>80</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G12" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H12" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I12" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J12" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="G12" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H12" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I12" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J12" t="s" s="2">
-        <v>89</v>
-      </c>
       <c r="K12" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="L12" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="M12" t="s" s="2">
         <v>147</v>
       </c>
-      <c r="L12" t="s" s="2">
+      <c r="N12" t="s" s="2">
         <v>148</v>
       </c>
-      <c r="M12" t="s" s="2">
+      <c r="O12" t="s" s="2">
         <v>149</v>
-      </c>
-      <c r="N12" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="O12" t="s" s="2">
-        <v>151</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>80</v>
@@ -3732,7 +3727,7 @@
         <v>80</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
@@ -3744,27 +3739,27 @@
         <v>80</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK12" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AL12" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="AM12" t="s" s="2">
         <v>155</v>
       </c>
-      <c r="AL12" t="s" s="2">
+      <c r="AN12" t="s" s="2">
         <v>156</v>
-      </c>
-      <c r="AM12" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="AN12" t="s" s="2">
-        <v>158</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3775,7 +3770,7 @@
         <v>78</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>80</v>
@@ -3787,13 +3782,13 @@
         <v>80</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>90</v>
+        <v>161</v>
       </c>
       <c r="L13" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="M13" t="s" s="2">
         <v>163</v>
-      </c>
-      <c r="M13" t="s" s="2">
-        <v>164</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -3844,25 +3839,25 @@
         <v>80</v>
       </c>
       <c r="AF13" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="AG13" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH13" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI13" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ13" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK13" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL13" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="AG13" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH13" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI13" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ13" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AK13" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL13" t="s" s="2">
-        <v>166</v>
       </c>
       <c r="AM13" t="s" s="2">
         <v>80</v>
@@ -3873,14 +3868,14 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="B14" t="s" s="2">
         <v>167</v>
-      </c>
-      <c r="B14" t="s" s="2">
-        <v>168</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
@@ -3899,16 +3894,16 @@
         <v>80</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="L14" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="M14" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="N14" t="s" s="2">
         <v>136</v>
-      </c>
-      <c r="M14" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>138</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3946,19 +3941,19 @@
         <v>80</v>
       </c>
       <c r="AB14" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="AC14" t="s" s="2">
         <v>170</v>
       </c>
-      <c r="AC14" t="s" s="2">
+      <c r="AD14" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE14" t="s" s="2">
         <v>171</v>
       </c>
-      <c r="AD14" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE14" t="s" s="2">
+      <c r="AF14" t="s" s="2">
         <v>172</v>
-      </c>
-      <c r="AF14" t="s" s="2">
-        <v>173</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -3970,13 +3965,13 @@
         <v>80</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AM14" t="s" s="2">
         <v>80</v>
@@ -3987,10 +3982,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="B15" t="s" s="2">
         <v>174</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>175</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -4001,31 +3996,31 @@
         <v>78</v>
       </c>
       <c r="G15" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H15" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I15" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="H15" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I15" t="s" s="2">
-        <v>89</v>
-      </c>
       <c r="J15" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="L15" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="M15" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="M15" t="s" s="2">
+      <c r="N15" t="s" s="2">
         <v>177</v>
       </c>
-      <c r="N15" t="s" s="2">
+      <c r="O15" t="s" s="2">
         <v>178</v>
-      </c>
-      <c r="O15" t="s" s="2">
-        <v>179</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>80</v>
@@ -4050,9 +4045,11 @@
         <v>80</v>
       </c>
       <c r="X15" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="Y15" t="s" s="2">
         <v>180</v>
       </c>
-      <c r="Y15" s="2"/>
       <c r="Z15" t="s" s="2">
         <v>181</v>
       </c>
@@ -4078,13 +4075,13 @@
         <v>78</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>80</v>
@@ -4096,7 +4093,7 @@
         <v>80</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="16" hidden="true">
@@ -4115,16 +4112,16 @@
         <v>78</v>
       </c>
       <c r="G16" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J16" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="H16" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I16" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J16" t="s" s="2">
-        <v>89</v>
       </c>
       <c r="K16" t="s" s="2">
         <v>186</v>
@@ -4166,9 +4163,11 @@
       <c r="X16" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="Y16" s="2"/>
+      <c r="Y16" t="s" s="2">
+        <v>192</v>
+      </c>
       <c r="Z16" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>80</v>
@@ -4186,19 +4185,19 @@
         <v>80</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>80</v>
@@ -4210,15 +4209,15 @@
         <v>80</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4229,7 +4228,7 @@
         <v>78</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>80</v>
@@ -4241,13 +4240,13 @@
         <v>80</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>90</v>
+        <v>161</v>
       </c>
       <c r="L17" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>163</v>
-      </c>
-      <c r="M17" t="s" s="2">
-        <v>164</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -4298,25 +4297,25 @@
         <v>80</v>
       </c>
       <c r="AF17" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="AG17" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH17" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI17" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ17" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK17" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL17" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="AG17" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH17" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI17" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ17" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AK17" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL17" t="s" s="2">
-        <v>166</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>80</v>
@@ -4327,14 +4326,14 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -4353,16 +4352,16 @@
         <v>80</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="L18" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="M18" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="N18" t="s" s="2">
         <v>136</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>138</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -4400,19 +4399,19 @@
         <v>80</v>
       </c>
       <c r="AB18" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="AC18" t="s" s="2">
         <v>170</v>
       </c>
-      <c r="AC18" t="s" s="2">
+      <c r="AD18" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE18" t="s" s="2">
         <v>171</v>
       </c>
-      <c r="AD18" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE18" t="s" s="2">
+      <c r="AF18" t="s" s="2">
         <v>172</v>
-      </c>
-      <c r="AF18" t="s" s="2">
-        <v>173</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -4424,13 +4423,13 @@
         <v>80</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>80</v>
@@ -4441,10 +4440,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4464,22 +4463,22 @@
         <v>80</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>80</v>
@@ -4528,7 +4527,7 @@
         <v>80</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -4540,27 +4539,27 @@
         <v>80</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4571,7 +4570,7 @@
         <v>78</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>80</v>
@@ -4583,13 +4582,13 @@
         <v>80</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>90</v>
+        <v>161</v>
       </c>
       <c r="L20" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="M20" t="s" s="2">
         <v>163</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>164</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4640,25 +4639,25 @@
         <v>80</v>
       </c>
       <c r="AF20" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="AG20" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH20" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL20" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="AG20" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH20" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AK20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL20" t="s" s="2">
-        <v>166</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>80</v>
@@ -4669,14 +4668,14 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -4695,16 +4694,16 @@
         <v>80</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="L21" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="M21" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="N21" t="s" s="2">
         <v>136</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>138</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4742,19 +4741,19 @@
         <v>80</v>
       </c>
       <c r="AB21" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="AC21" t="s" s="2">
         <v>170</v>
       </c>
-      <c r="AC21" t="s" s="2">
+      <c r="AD21" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE21" t="s" s="2">
         <v>171</v>
       </c>
-      <c r="AD21" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE21" t="s" s="2">
+      <c r="AF21" t="s" s="2">
         <v>172</v>
-      </c>
-      <c r="AF21" t="s" s="2">
-        <v>173</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -4766,13 +4765,13 @@
         <v>80</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>80</v>
@@ -4783,10 +4782,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4797,31 +4796,31 @@
         <v>78</v>
       </c>
       <c r="G22" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J22" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="H22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J22" t="s" s="2">
-        <v>89</v>
-      </c>
       <c r="K22" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>80</v>
@@ -4831,7 +4830,7 @@
         <v>80</v>
       </c>
       <c r="S22" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="T22" t="s" s="2">
         <v>80</v>
@@ -4870,39 +4869,39 @@
         <v>80</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4913,19 +4912,19 @@
         <v>78</v>
       </c>
       <c r="G23" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H23" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I23" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J23" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="H23" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I23" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J23" t="s" s="2">
-        <v>89</v>
-      </c>
       <c r="K23" t="s" s="2">
-        <v>225</v>
+        <v>161</v>
       </c>
       <c r="L23" t="s" s="2">
         <v>226</v>
@@ -4990,13 +4989,13 @@
         <v>78</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>80</v>
@@ -5027,19 +5026,19 @@
         <v>78</v>
       </c>
       <c r="G24" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H24" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I24" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J24" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="H24" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I24" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J24" t="s" s="2">
-        <v>89</v>
-      </c>
       <c r="K24" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="L24" t="s" s="2">
         <v>234</v>
@@ -5059,7 +5058,7 @@
         <v>80</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>80</v>
@@ -5104,13 +5103,13 @@
         <v>78</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>80</v>
@@ -5141,19 +5140,19 @@
         <v>78</v>
       </c>
       <c r="G25" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J25" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="H25" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I25" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J25" t="s" s="2">
-        <v>89</v>
-      </c>
       <c r="K25" t="s" s="2">
-        <v>225</v>
+        <v>161</v>
       </c>
       <c r="L25" t="s" s="2">
         <v>242</v>
@@ -5218,13 +5217,13 @@
         <v>78</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>80</v>
@@ -5255,16 +5254,16 @@
         <v>78</v>
       </c>
       <c r="G26" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H26" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I26" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J26" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="H26" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I26" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J26" t="s" s="2">
-        <v>89</v>
       </c>
       <c r="K26" t="s" s="2">
         <v>251</v>
@@ -5334,13 +5333,13 @@
         <v>78</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>80</v>
@@ -5371,19 +5370,19 @@
         <v>78</v>
       </c>
       <c r="G27" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J27" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="H27" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I27" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J27" t="s" s="2">
-        <v>89</v>
-      </c>
       <c r="K27" t="s" s="2">
-        <v>225</v>
+        <v>161</v>
       </c>
       <c r="L27" t="s" s="2">
         <v>261</v>
@@ -5450,13 +5449,13 @@
         <v>78</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>80</v>
@@ -5484,22 +5483,22 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G28" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J28" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="G28" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H28" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I28" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J28" t="s" s="2">
-        <v>89</v>
-      </c>
       <c r="K28" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L28" t="s" s="2">
         <v>271</v>
@@ -5566,13 +5565,13 @@
         <v>78</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>80</v>
@@ -5600,22 +5599,22 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G29" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H29" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I29" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J29" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="G29" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H29" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I29" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J29" t="s" s="2">
-        <v>89</v>
-      </c>
       <c r="K29" t="s" s="2">
-        <v>225</v>
+        <v>161</v>
       </c>
       <c r="L29" t="s" s="2">
         <v>282</v>
@@ -5680,13 +5679,13 @@
         <v>78</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>80</v>
@@ -5717,16 +5716,16 @@
         <v>78</v>
       </c>
       <c r="G30" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H30" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I30" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J30" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="H30" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I30" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J30" t="s" s="2">
-        <v>89</v>
       </c>
       <c r="K30" t="s" s="2">
         <v>291</v>
@@ -5792,13 +5791,13 @@
         <v>78</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>80</v>
@@ -5829,16 +5828,16 @@
         <v>78</v>
       </c>
       <c r="G31" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H31" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I31" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J31" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="H31" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I31" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J31" t="s" s="2">
-        <v>89</v>
       </c>
       <c r="K31" t="s" s="2">
         <v>299</v>
@@ -5906,13 +5905,13 @@
         <v>78</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>80</v>
@@ -5952,7 +5951,7 @@
         <v>80</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K32" t="s" s="2">
         <v>307</v>
@@ -6024,7 +6023,7 @@
         <v>80</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>310</v>
@@ -6064,10 +6063,10 @@
         <v>80</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L33" t="s" s="2">
         <v>313</v>
@@ -6138,7 +6137,7 @@
         <v>80</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>316</v>
@@ -6178,7 +6177,7 @@
         <v>80</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K34" t="s" s="2">
         <v>319</v>
@@ -6252,7 +6251,7 @@
         <v>80</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>323</v>
@@ -6292,7 +6291,7 @@
         <v>80</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K35" t="s" s="2">
         <v>319</v>
@@ -6368,7 +6367,7 @@
         <v>80</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>330</v>
@@ -6408,7 +6407,7 @@
         <v>80</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K36" t="s" s="2">
         <v>319</v>
@@ -6482,7 +6481,7 @@
         <v>80</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>80</v>
@@ -6510,22 +6509,22 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G37" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I37" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="G37" t="s" s="2">
+      <c r="J37" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="H37" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I37" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="J37" t="s" s="2">
-        <v>89</v>
-      </c>
       <c r="K37" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="L37" t="s" s="2">
         <v>336</v>
@@ -6562,7 +6561,7 @@
         <v>80</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Y37" t="s" s="2">
         <v>337</v>
@@ -6589,16 +6588,16 @@
         <v>335</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>341</v>
@@ -6626,22 +6625,22 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G38" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I38" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="G38" t="s" s="2">
+      <c r="J38" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="H38" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I38" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="J38" t="s" s="2">
-        <v>89</v>
-      </c>
       <c r="K38" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="L38" t="s" s="2">
         <v>346</v>
@@ -6678,7 +6677,7 @@
         <v>80</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Y38" t="s" s="2">
         <v>350</v>
@@ -6705,16 +6704,16 @@
         <v>345</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>352</v>
@@ -6754,7 +6753,7 @@
         <v>80</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K39" t="s" s="2">
         <v>186</v>
@@ -6830,7 +6829,7 @@
         <v>80</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>80</v>
@@ -6861,19 +6860,19 @@
         <v>78</v>
       </c>
       <c r="G40" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H40" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I40" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J40" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="H40" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I40" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J40" t="s" s="2">
-        <v>89</v>
-      </c>
       <c r="K40" t="s" s="2">
-        <v>225</v>
+        <v>161</v>
       </c>
       <c r="L40" t="s" s="2">
         <v>363</v>
@@ -6936,13 +6935,13 @@
         <v>78</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>80</v>
@@ -6973,19 +6972,19 @@
         <v>78</v>
       </c>
       <c r="G41" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H41" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I41" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J41" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="H41" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I41" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J41" t="s" s="2">
-        <v>89</v>
-      </c>
       <c r="K41" t="s" s="2">
-        <v>225</v>
+        <v>161</v>
       </c>
       <c r="L41" t="s" s="2">
         <v>366</v>
@@ -7050,13 +7049,13 @@
         <v>78</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>80</v>
@@ -7084,19 +7083,19 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G42" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H42" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I42" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J42" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="G42" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H42" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I42" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J42" t="s" s="2">
-        <v>89</v>
       </c>
       <c r="K42" t="s" s="2">
         <v>372</v>
@@ -7159,16 +7158,16 @@
         <v>370</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>375</v>
@@ -7196,19 +7195,19 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G43" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J43" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="G43" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H43" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I43" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J43" t="s" s="2">
-        <v>89</v>
       </c>
       <c r="K43" t="s" s="2">
         <v>380</v>
@@ -7276,13 +7275,13 @@
         <v>78</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>384</v>
@@ -7310,19 +7309,19 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G44" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J44" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="G44" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H44" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I44" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J44" t="s" s="2">
-        <v>89</v>
       </c>
       <c r="K44" t="s" s="2">
         <v>291</v>
@@ -7392,13 +7391,13 @@
         <v>78</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>394</v>
@@ -7429,16 +7428,16 @@
         <v>78</v>
       </c>
       <c r="G45" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J45" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="H45" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I45" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J45" t="s" s="2">
-        <v>89</v>
       </c>
       <c r="K45" t="s" s="2">
         <v>400</v>
@@ -7504,13 +7503,13 @@
         <v>78</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>403</v>
@@ -7541,16 +7540,16 @@
         <v>78</v>
       </c>
       <c r="G46" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J46" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="H46" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I46" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J46" t="s" s="2">
-        <v>89</v>
       </c>
       <c r="K46" t="s" s="2">
         <v>407</v>
@@ -7618,13 +7617,13 @@
         <v>78</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>411</v>
@@ -7738,7 +7737,7 @@
         <v>80</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>80</v>
@@ -7852,7 +7851,7 @@
         <v>80</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>422</v>
@@ -7892,7 +7891,7 @@
         <v>80</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K49" t="s" s="2">
         <v>425</v>
@@ -7968,7 +7967,7 @@
         <v>80</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>430</v>
@@ -8084,7 +8083,7 @@
         <v>80</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>440</v>
@@ -8200,7 +8199,7 @@
         <v>80</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>80</v>
@@ -8228,7 +8227,7 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G52" t="s" s="2">
         <v>79</v>
@@ -8345,7 +8344,7 @@
         <v>78</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>80</v>
@@ -8357,13 +8356,13 @@
         <v>80</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>225</v>
+        <v>161</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>163</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>164</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8414,25 +8413,25 @@
         <v>80</v>
       </c>
       <c r="AF53" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="AG53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH53" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL53" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="AG53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH53" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI53" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ53" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AK53" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL53" t="s" s="2">
-        <v>166</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>80</v>
@@ -8450,7 +8449,7 @@
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8469,16 +8468,16 @@
         <v>80</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="M54" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="N54" t="s" s="2">
         <v>136</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>138</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8528,7 +8527,7 @@
         <v>80</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -8540,13 +8539,13 @@
         <v>80</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>80</v>
@@ -8577,13 +8576,13 @@
         <v>80</v>
       </c>
       <c r="I55" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="L55" t="s" s="2">
         <v>460</v>
@@ -8592,10 +8591,10 @@
         <v>461</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>80</v>
@@ -8656,13 +8655,13 @@
         <v>80</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>80</v>
@@ -8770,7 +8769,7 @@
         <v>80</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>80</v>
@@ -8886,7 +8885,7 @@
         <v>80</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>474</v>
@@ -9002,7 +9001,7 @@
         <v>80</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>80</v>
@@ -9033,7 +9032,7 @@
         <v>78</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>80</v>
@@ -9112,13 +9111,13 @@
         <v>78</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>490</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>491</v>
@@ -9149,7 +9148,7 @@
         <v>78</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>80</v>
@@ -9226,7 +9225,7 @@
         <v>78</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>490</v>
@@ -9263,7 +9262,7 @@
         <v>78</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>80</v>
@@ -9275,13 +9274,13 @@
         <v>80</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>225</v>
+        <v>161</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="M61" t="s" s="2">
         <v>163</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>164</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9332,25 +9331,25 @@
         <v>80</v>
       </c>
       <c r="AF61" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="AG61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH61" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL61" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="AG61" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH61" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AK61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL61" t="s" s="2">
-        <v>166</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>80</v>
@@ -9387,7 +9386,7 @@
         <v>80</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="L62" t="s" s="2">
         <v>499</v>
@@ -9432,17 +9431,17 @@
         <v>80</v>
       </c>
       <c r="AB62" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AC62" s="2"/>
       <c r="AD62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE62" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="AF62" t="s" s="2">
         <v>172</v>
-      </c>
-      <c r="AF62" t="s" s="2">
-        <v>173</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -9454,7 +9453,7 @@
         <v>80</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>80</v>
@@ -9487,10 +9486,10 @@
         <v>78</v>
       </c>
       <c r="G63" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H63" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="H63" t="s" s="2">
-        <v>89</v>
       </c>
       <c r="I63" t="s" s="2">
         <v>80</v>
@@ -9556,7 +9555,7 @@
         <v>80</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -9568,7 +9567,7 @@
         <v>506</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>507</v>
+        <v>138</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>80</v>
@@ -9585,10 +9584,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9605,13 +9604,13 @@
         <v>80</v>
       </c>
       <c r="I64" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="L64" t="s" s="2">
         <v>460</v>
@@ -9620,10 +9619,10 @@
         <v>461</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>80</v>
@@ -9684,13 +9683,13 @@
         <v>80</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>80</v>
@@ -9701,10 +9700,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9715,11 +9714,11 @@
         <v>78</v>
       </c>
       <c r="G65" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H65" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="H65" t="s" s="2">
-        <v>89</v>
-      </c>
       <c r="I65" t="s" s="2">
         <v>80</v>
       </c>
@@ -9727,17 +9726,17 @@
         <v>80</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="L65" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="M65" t="s" s="2">
         <v>510</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>511</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>80</v>
@@ -9747,64 +9746,64 @@
         <v>80</v>
       </c>
       <c r="S65" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="Y65" t="s" s="2">
         <v>513</v>
       </c>
-      <c r="T65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X65" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="Y65" t="s" s="2">
+      <c r="Z65" t="s" s="2">
         <v>514</v>
       </c>
-      <c r="Z65" t="s" s="2">
+      <c r="AA65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF65" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL65" t="s" s="2">
         <v>515</v>
-      </c>
-      <c r="AA65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF65" t="s" s="2">
-        <v>509</v>
-      </c>
-      <c r="AG65" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH65" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ65" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL65" t="s" s="2">
-        <v>516</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>80</v>
@@ -9815,10 +9814,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9841,17 +9840,17 @@
         <v>80</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="L66" t="s" s="2">
         <v>308</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>80</v>
@@ -9900,7 +9899,7 @@
         <v>80</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -9912,7 +9911,7 @@
         <v>80</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>310</v>
@@ -9929,10 +9928,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9955,19 +9954,19 @@
         <v>80</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L67" t="s" s="2">
         <v>313</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N67" t="s" s="2">
         <v>315</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>80</v>
@@ -10016,7 +10015,7 @@
         <v>80</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
@@ -10028,7 +10027,7 @@
         <v>80</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>316</v>
@@ -10045,10 +10044,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10059,10 +10058,10 @@
         <v>78</v>
       </c>
       <c r="G68" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H68" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="H68" t="s" s="2">
-        <v>89</v>
       </c>
       <c r="I68" t="s" s="2">
         <v>80</v>
@@ -10074,16 +10073,16 @@
         <v>186</v>
       </c>
       <c r="L68" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="M68" t="s" s="2">
         <v>524</v>
       </c>
-      <c r="M68" t="s" s="2">
+      <c r="N68" t="s" s="2">
         <v>525</v>
       </c>
-      <c r="N68" t="s" s="2">
+      <c r="O68" t="s" s="2">
         <v>526</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>527</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>80</v>
@@ -10108,61 +10107,61 @@
         <v>80</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Y68" s="2"/>
       <c r="Z68" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF68" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="AG68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH68" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK68" t="s" s="2">
         <v>528</v>
       </c>
-      <c r="AA68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF68" t="s" s="2">
-        <v>523</v>
-      </c>
-      <c r="AG68" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH68" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ68" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK68" t="s" s="2">
+      <c r="AL68" t="s" s="2">
         <v>529</v>
       </c>
-      <c r="AL68" t="s" s="2">
+      <c r="AM68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN68" t="s" s="2">
         <v>530</v>
-      </c>
-      <c r="AM68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN68" t="s" s="2">
-        <v>531</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10173,7 +10172,7 @@
         <v>78</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>80</v>
@@ -10185,13 +10184,13 @@
         <v>80</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>90</v>
+        <v>161</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="M69" t="s" s="2">
         <v>163</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>164</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10242,25 +10241,25 @@
         <v>80</v>
       </c>
       <c r="AF69" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL69" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="AG69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH69" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AK69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL69" t="s" s="2">
-        <v>166</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>80</v>
@@ -10271,14 +10270,14 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -10297,16 +10296,16 @@
         <v>80</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="N70" t="s" s="2">
         <v>136</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>138</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -10344,19 +10343,19 @@
         <v>80</v>
       </c>
       <c r="AB70" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="AC70" t="s" s="2">
         <v>170</v>
       </c>
-      <c r="AC70" t="s" s="2">
+      <c r="AD70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE70" t="s" s="2">
         <v>171</v>
       </c>
-      <c r="AD70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE70" t="s" s="2">
+      <c r="AF70" t="s" s="2">
         <v>172</v>
-      </c>
-      <c r="AF70" t="s" s="2">
-        <v>173</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -10368,13 +10367,13 @@
         <v>80</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>80</v>
@@ -10385,10 +10384,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10408,22 +10407,22 @@
         <v>80</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>80</v>
@@ -10472,7 +10471,7 @@
         <v>80</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
@@ -10484,27 +10483,27 @@
         <v>80</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10515,19 +10514,19 @@
         <v>78</v>
       </c>
       <c r="G72" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J72" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="H72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J72" t="s" s="2">
-        <v>89</v>
-      </c>
       <c r="K72" t="s" s="2">
-        <v>225</v>
+        <v>161</v>
       </c>
       <c r="L72" t="s" s="2">
         <v>261</v>
@@ -10549,7 +10548,7 @@
         <v>80</v>
       </c>
       <c r="S72" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="T72" t="s" s="2">
         <v>80</v>
@@ -10594,13 +10593,13 @@
         <v>78</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>80</v>
@@ -10617,10 +10616,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10631,10 +10630,10 @@
         <v>78</v>
       </c>
       <c r="G73" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H73" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="H73" t="s" s="2">
-        <v>89</v>
       </c>
       <c r="I73" t="s" s="2">
         <v>80</v>
@@ -10646,13 +10645,13 @@
         <v>186</v>
       </c>
       <c r="L73" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="M73" t="s" s="2">
         <v>538</v>
       </c>
-      <c r="M73" t="s" s="2">
+      <c r="N73" t="s" s="2">
         <v>539</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>540</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -10678,11 +10677,11 @@
         <v>80</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Y73" s="2"/>
       <c r="Z73" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>80</v>
@@ -10700,7 +10699,7 @@
         <v>80</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
@@ -10712,10 +10711,10 @@
         <v>80</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="AL73" t="s" s="2">
         <v>80</v>
@@ -10729,10 +10728,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10743,7 +10742,7 @@
         <v>78</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>80</v>
@@ -10755,13 +10754,13 @@
         <v>80</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>90</v>
+        <v>161</v>
       </c>
       <c r="L74" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="M74" t="s" s="2">
         <v>163</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>164</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -10812,25 +10811,25 @@
         <v>80</v>
       </c>
       <c r="AF74" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="AG74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH74" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL74" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="AG74" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH74" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI74" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ74" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AK74" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL74" t="s" s="2">
-        <v>166</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>80</v>
@@ -10841,14 +10840,14 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
@@ -10867,16 +10866,16 @@
         <v>80</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="N75" t="s" s="2">
         <v>136</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>138</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -10914,19 +10913,19 @@
         <v>80</v>
       </c>
       <c r="AB75" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="AC75" t="s" s="2">
         <v>170</v>
       </c>
-      <c r="AC75" t="s" s="2">
+      <c r="AD75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE75" t="s" s="2">
         <v>171</v>
       </c>
-      <c r="AD75" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE75" t="s" s="2">
+      <c r="AF75" t="s" s="2">
         <v>172</v>
-      </c>
-      <c r="AF75" t="s" s="2">
-        <v>173</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
@@ -10938,13 +10937,13 @@
         <v>80</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>80</v>
@@ -10955,10 +10954,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10978,22 +10977,22 @@
         <v>80</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>80</v>
@@ -11042,7 +11041,7 @@
         <v>80</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>78</v>
@@ -11054,27 +11053,27 @@
         <v>80</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11085,19 +11084,19 @@
         <v>78</v>
       </c>
       <c r="G77" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J77" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="H77" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I77" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J77" t="s" s="2">
-        <v>89</v>
-      </c>
       <c r="K77" t="s" s="2">
-        <v>225</v>
+        <v>161</v>
       </c>
       <c r="L77" t="s" s="2">
         <v>261</v>
@@ -11119,7 +11118,7 @@
         <v>80</v>
       </c>
       <c r="S77" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="T77" t="s" s="2">
         <v>80</v>
@@ -11164,13 +11163,13 @@
         <v>78</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>80</v>
@@ -11187,10 +11186,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11213,16 +11212,16 @@
         <v>80</v>
       </c>
       <c r="K78" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="L78" t="s" s="2">
         <v>549</v>
       </c>
-      <c r="L78" t="s" s="2">
+      <c r="M78" t="s" s="2">
         <v>550</v>
       </c>
-      <c r="M78" t="s" s="2">
+      <c r="N78" t="s" s="2">
         <v>551</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>552</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -11272,7 +11271,7 @@
         <v>80</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
@@ -11284,7 +11283,7 @@
         <v>80</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>430</v>
@@ -11301,10 +11300,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11330,14 +11329,14 @@
         <v>442</v>
       </c>
       <c r="L79" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="M79" t="s" s="2">
         <v>554</v>
-      </c>
-      <c r="M79" t="s" s="2">
-        <v>555</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>80</v>
@@ -11386,7 +11385,7 @@
         <v>80</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
@@ -11398,7 +11397,7 @@
         <v>80</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>80</v>
@@ -11415,10 +11414,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11426,34 +11425,34 @@
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G80" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I80" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="G80" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H80" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I80" t="s" s="2">
-        <v>89</v>
-      </c>
       <c r="J80" t="s" s="2">
         <v>80</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="L80" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="M80" t="s" s="2">
         <v>558</v>
       </c>
-      <c r="M80" t="s" s="2">
+      <c r="N80" t="s" s="2">
         <v>559</v>
       </c>
-      <c r="N80" t="s" s="2">
+      <c r="O80" t="s" s="2">
         <v>560</v>
-      </c>
-      <c r="O80" t="s" s="2">
-        <v>561</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>80</v>
@@ -11478,63 +11477,63 @@
         <v>80</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Y80" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="Z80" t="s" s="2">
         <v>562</v>
       </c>
-      <c r="Z80" t="s" s="2">
+      <c r="AA80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF80" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="AG80" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AH80" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ80" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK80" t="s" s="2">
         <v>563</v>
       </c>
-      <c r="AA80" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB80" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC80" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD80" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE80" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF80" t="s" s="2">
-        <v>557</v>
-      </c>
-      <c r="AG80" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AH80" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI80" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ80" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK80" t="s" s="2">
+      <c r="AL80" t="s" s="2">
         <v>564</v>
       </c>
-      <c r="AL80" t="s" s="2">
+      <c r="AM80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN80" t="s" s="2">
         <v>565</v>
-      </c>
-      <c r="AM80" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN80" t="s" s="2">
-        <v>566</v>
       </c>
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11545,7 +11544,7 @@
         <v>78</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>80</v>
@@ -11560,13 +11559,13 @@
         <v>186</v>
       </c>
       <c r="L81" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="M81" t="s" s="2">
         <v>568</v>
       </c>
-      <c r="M81" t="s" s="2">
+      <c r="N81" t="s" s="2">
         <v>569</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>570</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -11616,22 +11615,22 @@
         <v>80</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="AL81" t="s" s="2">
         <v>80</v>
@@ -11645,10 +11644,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11659,13 +11658,13 @@
         <v>78</v>
       </c>
       <c r="G82" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I82" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="H82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I82" t="s" s="2">
-        <v>89</v>
       </c>
       <c r="J82" t="s" s="2">
         <v>80</v>
@@ -11674,85 +11673,85 @@
         <v>251</v>
       </c>
       <c r="L82" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="M82" t="s" s="2">
         <v>573</v>
       </c>
-      <c r="M82" t="s" s="2">
+      <c r="N82" t="s" s="2">
         <v>574</v>
       </c>
-      <c r="N82" t="s" s="2">
+      <c r="O82" t="s" s="2">
         <v>575</v>
       </c>
-      <c r="O82" t="s" s="2">
+      <c r="P82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q82" t="s" s="2">
         <v>576</v>
       </c>
-      <c r="P82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q82" t="s" s="2">
+      <c r="R82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF82" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="AG82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH82" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ82" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK82" t="s" s="2">
         <v>577</v>
       </c>
-      <c r="R82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF82" t="s" s="2">
-        <v>572</v>
-      </c>
-      <c r="AG82" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH82" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ82" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK82" t="s" s="2">
+      <c r="AL82" t="s" s="2">
         <v>578</v>
-      </c>
-      <c r="AL82" t="s" s="2">
-        <v>579</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>80</v>
@@ -11763,10 +11762,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11777,7 +11776,7 @@
         <v>78</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>80</v>
@@ -11789,17 +11788,17 @@
         <v>80</v>
       </c>
       <c r="K83" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="L83" t="s" s="2">
         <v>581</v>
       </c>
-      <c r="L83" t="s" s="2">
+      <c r="M83" t="s" s="2">
         <v>582</v>
-      </c>
-      <c r="M83" t="s" s="2">
-        <v>583</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>80</v>
@@ -11836,29 +11835,29 @@
         <v>80</v>
       </c>
       <c r="AB83" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="AC83" s="2"/>
       <c r="AD83" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE83" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>394</v>
@@ -11870,18 +11869,18 @@
         <v>80</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="B84" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="C84" t="s" s="2">
         <v>587</v>
-      </c>
-      <c r="B84" t="s" s="2">
-        <v>580</v>
-      </c>
-      <c r="C84" t="s" s="2">
-        <v>588</v>
       </c>
       <c r="D84" t="s" s="2">
         <v>80</v>
@@ -11891,7 +11890,7 @@
         <v>78</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>80</v>
@@ -11906,14 +11905,14 @@
         <v>291</v>
       </c>
       <c r="L84" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="M84" t="s" s="2">
         <v>582</v>
-      </c>
-      <c r="M84" t="s" s="2">
-        <v>583</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>80</v>
@@ -11962,19 +11961,19 @@
         <v>80</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>394</v>
@@ -11986,15 +11985,15 @@
         <v>80</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12005,7 +12004,7 @@
         <v>78</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>80</v>
@@ -12017,19 +12016,19 @@
         <v>80</v>
       </c>
       <c r="K85" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="L85" t="s" s="2">
         <v>590</v>
       </c>
-      <c r="L85" t="s" s="2">
+      <c r="M85" t="s" s="2">
         <v>591</v>
       </c>
-      <c r="M85" t="s" s="2">
+      <c r="N85" t="s" s="2">
         <v>592</v>
       </c>
-      <c r="N85" t="s" s="2">
+      <c r="O85" t="s" s="2">
         <v>593</v>
-      </c>
-      <c r="O85" t="s" s="2">
-        <v>594</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>80</v>
@@ -12078,39 +12077,39 @@
         <v>80</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL85" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="AM85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN85" t="s" s="2">
         <v>595</v>
-      </c>
-      <c r="AM85" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN85" t="s" s="2">
-        <v>596</v>
       </c>
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12133,19 +12132,19 @@
         <v>80</v>
       </c>
       <c r="K86" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="L86" t="s" s="2">
         <v>598</v>
       </c>
-      <c r="L86" t="s" s="2">
+      <c r="M86" t="s" s="2">
         <v>599</v>
       </c>
-      <c r="M86" t="s" s="2">
+      <c r="N86" t="s" s="2">
         <v>600</v>
       </c>
-      <c r="N86" t="s" s="2">
-        <v>601</v>
-      </c>
       <c r="O86" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>80</v>
@@ -12194,7 +12193,7 @@
         <v>80</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>78</v>
@@ -12206,27 +12205,27 @@
         <v>80</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK86" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="AL86" t="s" s="2">
         <v>602</v>
       </c>
-      <c r="AL86" t="s" s="2">
+      <c r="AM86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN86" t="s" s="2">
         <v>603</v>
-      </c>
-      <c r="AM86" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN86" t="s" s="2">
-        <v>604</v>
       </c>
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12237,7 +12236,7 @@
         <v>78</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>80</v>
@@ -12249,13 +12248,13 @@
         <v>80</v>
       </c>
       <c r="K87" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="L87" t="s" s="2">
         <v>606</v>
       </c>
-      <c r="L87" t="s" s="2">
+      <c r="M87" t="s" s="2">
         <v>607</v>
-      </c>
-      <c r="M87" t="s" s="2">
-        <v>608</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -12285,61 +12284,61 @@
         <v>358</v>
       </c>
       <c r="Y87" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="Z87" t="s" s="2">
         <v>609</v>
       </c>
-      <c r="Z87" t="s" s="2">
-        <v>610</v>
-      </c>
       <c r="AA87" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AB87" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="AC87" s="2"/>
       <c r="AD87" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE87" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL87" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="AM87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN87" t="s" s="2">
         <v>611</v>
-      </c>
-      <c r="AM87" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN87" t="s" s="2">
-        <v>612</v>
       </c>
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="B88" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="C88" t="s" s="2">
         <v>613</v>
-      </c>
-      <c r="B88" t="s" s="2">
-        <v>605</v>
-      </c>
-      <c r="C88" t="s" s="2">
-        <v>614</v>
       </c>
       <c r="D88" t="s" s="2">
         <v>80</v>
@@ -12349,10 +12348,10 @@
         <v>78</v>
       </c>
       <c r="G88" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H88" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="H88" t="s" s="2">
-        <v>89</v>
       </c>
       <c r="I88" t="s" s="2">
         <v>80</v>
@@ -12364,10 +12363,10 @@
         <v>186</v>
       </c>
       <c r="L88" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="M88" t="s" s="2">
         <v>607</v>
-      </c>
-      <c r="M88" t="s" s="2">
-        <v>608</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -12394,11 +12393,11 @@
         <v>80</v>
       </c>
       <c r="X88" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Y88" s="2"/>
       <c r="Z88" t="s" s="2">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>80</v>
@@ -12416,39 +12415,39 @@
         <v>80</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL88" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="AM88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN88" t="s" s="2">
         <v>611</v>
-      </c>
-      <c r="AM88" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN88" t="s" s="2">
-        <v>612</v>
       </c>
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="B89" t="s" s="2">
         <v>616</v>
-      </c>
-      <c r="B89" t="s" s="2">
-        <v>617</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12459,7 +12458,7 @@
         <v>78</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>80</v>
@@ -12471,13 +12470,13 @@
         <v>80</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>90</v>
+        <v>161</v>
       </c>
       <c r="L89" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="M89" t="s" s="2">
         <v>163</v>
-      </c>
-      <c r="M89" t="s" s="2">
-        <v>164</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -12528,25 +12527,25 @@
         <v>80</v>
       </c>
       <c r="AF89" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="AG89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH89" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL89" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="AG89" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH89" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI89" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ89" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AK89" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL89" t="s" s="2">
-        <v>166</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>80</v>
@@ -12557,14 +12556,14 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="B90" t="s" s="2">
         <v>618</v>
-      </c>
-      <c r="B90" t="s" s="2">
-        <v>619</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
@@ -12583,16 +12582,16 @@
         <v>80</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="L90" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="M90" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="N90" t="s" s="2">
         <v>136</v>
-      </c>
-      <c r="M90" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="N90" t="s" s="2">
-        <v>138</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -12630,19 +12629,19 @@
         <v>80</v>
       </c>
       <c r="AB90" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="AC90" t="s" s="2">
         <v>170</v>
       </c>
-      <c r="AC90" t="s" s="2">
+      <c r="AD90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE90" t="s" s="2">
         <v>171</v>
       </c>
-      <c r="AD90" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE90" t="s" s="2">
+      <c r="AF90" t="s" s="2">
         <v>172</v>
-      </c>
-      <c r="AF90" t="s" s="2">
-        <v>173</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>78</v>
@@ -12654,13 +12653,13 @@
         <v>80</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>80</v>
@@ -12671,10 +12670,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="B91" t="s" s="2">
         <v>620</v>
-      </c>
-      <c r="B91" t="s" s="2">
-        <v>621</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12694,22 +12693,22 @@
         <v>80</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>80</v>
@@ -12758,7 +12757,7 @@
         <v>80</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>78</v>
@@ -12770,27 +12769,27 @@
         <v>80</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="B92" t="s" s="2">
         <v>622</v>
-      </c>
-      <c r="B92" t="s" s="2">
-        <v>623</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12801,19 +12800,19 @@
         <v>78</v>
       </c>
       <c r="G92" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J92" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="H92" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I92" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J92" t="s" s="2">
-        <v>89</v>
-      </c>
       <c r="K92" t="s" s="2">
-        <v>225</v>
+        <v>161</v>
       </c>
       <c r="L92" t="s" s="2">
         <v>261</v>
@@ -12835,7 +12834,7 @@
         <v>80</v>
       </c>
       <c r="S92" t="s" s="2">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="T92" t="s" s="2">
         <v>80</v>
@@ -12880,13 +12879,13 @@
         <v>78</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AI92" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK92" t="s" s="2">
         <v>80</v>
@@ -12903,21 +12902,21 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>80</v>
@@ -12929,17 +12928,17 @@
         <v>80</v>
       </c>
       <c r="K93" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="L93" t="s" s="2">
         <v>627</v>
       </c>
-      <c r="L93" t="s" s="2">
+      <c r="M93" t="s" s="2">
         <v>628</v>
-      </c>
-      <c r="M93" t="s" s="2">
-        <v>629</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" t="s" s="2">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>80</v>
@@ -12988,39 +12987,39 @@
         <v>80</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AI93" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK93" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL93" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="AM93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN93" t="s" s="2">
         <v>631</v>
-      </c>
-      <c r="AM93" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN93" t="s" s="2">
-        <v>632</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13031,7 +13030,7 @@
         <v>78</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H94" t="s" s="2">
         <v>80</v>
@@ -13043,13 +13042,13 @@
         <v>80</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="L94" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="M94" t="s" s="2">
         <v>634</v>
-      </c>
-      <c r="M94" t="s" s="2">
-        <v>635</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -13100,39 +13099,39 @@
         <v>80</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AI94" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL94" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="AM94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN94" t="s" s="2">
         <v>636</v>
-      </c>
-      <c r="AM94" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN94" t="s" s="2">
-        <v>637</v>
       </c>
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13143,7 +13142,7 @@
         <v>78</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>80</v>
@@ -13155,13 +13154,13 @@
         <v>80</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>225</v>
+        <v>161</v>
       </c>
       <c r="L95" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="M95" t="s" s="2">
         <v>639</v>
-      </c>
-      <c r="M95" t="s" s="2">
-        <v>640</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -13212,25 +13211,25 @@
         <v>80</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AI95" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="AM95" t="s" s="2">
         <v>80</v>
@@ -13241,10 +13240,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13255,7 +13254,7 @@
         <v>78</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>80</v>
@@ -13270,14 +13269,14 @@
         <v>477</v>
       </c>
       <c r="L96" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="M96" t="s" s="2">
         <v>643</v>
-      </c>
-      <c r="M96" t="s" s="2">
-        <v>644</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" t="s" s="2">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>80</v>
@@ -13326,7 +13325,7 @@
         <v>80</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>78</v>
@@ -13338,10 +13337,10 @@
         <v>80</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="AL96" t="s" s="2">
         <v>482</v>

--- a/branches/Richard/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-09T15:34:42+00:00</t>
+    <t>2023-05-09T15:35:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
